--- a/Boom.xlsx
+++ b/Boom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fa46c21c18863703/3 Welt 2.0/1  laser drcker/Laser 3d printer realise/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{113FFE9C-36FE-4F76-8707-21AF19DF0BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C24432C3-AF6D-4744-9B4A-CAACC5DDCCB1}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{113FFE9C-36FE-4F76-8707-21AF19DF0BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB942D33-0905-419D-ACC8-A78EA534DCA8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="46296" windowHeight="25536" xr2:uid="{FC454746-5152-41EA-AF76-9CDCA9A4348A}"/>
+    <workbookView xWindow="7476" yWindow="5544" windowWidth="24636" windowHeight="17292" xr2:uid="{FC454746-5152-41EA-AF76-9CDCA9A4348A}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>BOM</t>
   </si>
@@ -129,6 +129,12 @@
   </si>
   <si>
     <t xml:space="preserve">https://a.aliexpress.com/_EjI898i </t>
+  </si>
+  <si>
+    <t>Laser Safety glasses for 450nm</t>
+  </si>
+  <si>
+    <t>To be safe from the lasers</t>
   </si>
 </sst>
 </file>
@@ -167,12 +173,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -203,12 +215,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -544,10 +558,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{224399D6-A3FC-4432-9E40-ACF56E306B7F}">
-  <dimension ref="B1:E10"/>
+  <dimension ref="B1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.109375" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
     <col min="3" max="3" width="52.109375" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" customWidth="1"/>
     <col min="5" max="5" width="44.33203125" customWidth="1"/>
@@ -573,124 +587,136 @@
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>7</v>
+      <c r="B3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{2E30D16F-E9CC-474B-B5DF-0BB8A7E911D9}"/>
-    <hyperlink ref="C7" r:id="rId2" xr:uid="{4E578B63-FAC2-4D31-90D1-FB602806550C}"/>
-    <hyperlink ref="C8" r:id="rId3" xr:uid="{46421246-B2A3-4C41-97A7-E2C886D3442D}"/>
-    <hyperlink ref="C3" r:id="rId4" xr:uid="{D3ABC564-8520-4D88-8A58-3D18D2A3C071}"/>
-    <hyperlink ref="C5" r:id="rId5" xr:uid="{150BA4CF-8474-4820-B3E0-E7755085DDE7}"/>
-    <hyperlink ref="C6" r:id="rId6" xr:uid="{6AEACB1B-1037-43BF-B5F3-24790F2F2CAC}"/>
-    <hyperlink ref="C9" r:id="rId7" xr:uid="{FCA0DC9C-542A-4A0D-95EE-337D5062637B}"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{2E30D16F-E9CC-474B-B5DF-0BB8A7E911D9}"/>
+    <hyperlink ref="C8" r:id="rId2" xr:uid="{4E578B63-FAC2-4D31-90D1-FB602806550C}"/>
+    <hyperlink ref="C9" r:id="rId3" xr:uid="{46421246-B2A3-4C41-97A7-E2C886D3442D}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{D3ABC564-8520-4D88-8A58-3D18D2A3C071}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{150BA4CF-8474-4820-B3E0-E7755085DDE7}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{6AEACB1B-1037-43BF-B5F3-24790F2F2CAC}"/>
+    <hyperlink ref="C10" r:id="rId7" xr:uid="{FCA0DC9C-542A-4A0D-95EE-337D5062637B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
